--- a/upload/julgamento_contas_governador.xlsx
+++ b/upload/julgamento_contas_governador.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>ano</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>https://www.almg.gov.br/atividade-parlamentar/leis/legislacao-mineira/?pesquisou=true&amp;aba=pesquisa&amp;q=APROVA+AS+CONTAS+DO+GOVERNADOR+DO+ESTADO+EXERC%C3%8DCIO&amp;grupo=&amp;num=&amp;ano=&amp;dataInicio=&amp;dataFim=&amp;sit=&amp;ordem=2</t>
+  </si>
+  <si>
+    <t>https://cge.mg.gov.br/auditoria-interna-governamental/relatorios-de-auditoria/category/129-relatorio-de-controle-interno-rci?download=1539:relatorio-de-controle-interno-n-1962306-contas-do-governo-exercicio-de-2025</t>
+  </si>
+  <si>
+    <t>https://www.tce.mg.gov.br/pesquisa_processo.asp?cod_processo=1210489</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="69.42578125" bestFit="1" customWidth="1"/>
@@ -474,203 +480,225 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2">
-        <v>1188127</v>
+        <v>1210489</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3">
-        <v>1167016</v>
+        <v>1188127</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
+      <c r="D3" t="s">
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4">
-        <v>1144601</v>
+        <v>1167016</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5">
-        <v>1114783</v>
+        <v>1144601</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B6">
-        <v>1101512</v>
+        <v>1114783</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B7">
-        <v>1088786</v>
+        <v>1101512</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8">
-        <v>1066559</v>
+        <v>1088786</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B9">
-        <v>1040601</v>
+        <v>1066559</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B10">
-        <v>1007713</v>
+        <v>1040601</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>28</v>
+      <c r="A11">
+        <v>2016</v>
+      </c>
+      <c r="B11">
+        <v>1007713</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D5" r:id="rId1"/>
+    <hyperlink ref="D4" r:id="rId2"/>
+    <hyperlink ref="F2" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>